--- a/output/pdf_financials_xlsx/CRUZ.xlsx
+++ b/output/pdf_financials_xlsx/CRUZ.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.101955</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.074806</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.025189</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.925342</v>
+        <v>-2.027297</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.305611</v>
+        <v>-1.380417</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.955391</v>
+        <v>-0.98058</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.868384</v>
+        <v>-1.970339</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.25041</v>
+        <v>-1.325216</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.900533</v>
+        <v>-0.925722</v>
       </c>
     </row>
     <row r="30">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRUZ.xlsx
+++ b/output/pdf_financials_xlsx/CRUZ.xlsx
@@ -812,20 +812,14 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="25">
@@ -834,20 +828,14 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1106,13 +1094,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.005687</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.06318600000000001</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>0.01997</v>
       </c>
     </row>
     <row r="42">
@@ -1218,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.014983</v>
+        <v>0.009296</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.084993</v>
+        <v>0.021807</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.037588</v>
+        <v>0.017618</v>
       </c>
     </row>
     <row r="49">
@@ -1384,13 +1372,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>3.562286</v>
+        <v>3.791193</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3.290815</v>
+        <v>3.464521</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2.790292</v>
+        <v>2.90914</v>
       </c>
     </row>
     <row r="59">
@@ -1432,13 +1420,13 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.308972</v>
+        <v>0.080065</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.255866</v>
+        <v>0.08216</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.201008</v>
+        <v>0.08216</v>
       </c>
     </row>
     <row r="62">
@@ -1544,13 +1532,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.268019</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.280358</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.250843</v>
       </c>
     </row>
     <row r="69">
@@ -1656,13 +1644,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.324478</v>
+        <v>0.056459</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.342199</v>
+        <v>0.061841</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.318571</v>
+        <v>0.067728</v>
       </c>
     </row>
     <row r="76">
@@ -1870,13 +1858,13 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>25.260027</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>25.886623</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>25.257223</v>
       </c>
     </row>
     <row r="89">
@@ -1934,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.149222</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.072826</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.072826</v>
       </c>
     </row>
     <row r="93">
@@ -2752,7 +2740,11 @@
           <t>Receivables – Notes 6 and 13</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -2843,7 +2835,11 @@
           <t>Property and equipment – Note 7</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -2899,7 +2895,11 @@
           <t>Right-of-use asset – Note 8</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3021,7 +3021,11 @@
           <t>Accounts payable and accrued liabilities – Notes 10 and 13 $</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3201,7 +3205,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3230,7 +3238,11 @@
           <t>Reserves – Note 11</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3385,7 +3397,11 @@
           <t>Receivables – Notes 5 and 12</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.005687</v>
       </c>
@@ -3414,7 +3430,11 @@
           <t>Property and equipment – Note 6</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.020935</v>
       </c>
@@ -3443,7 +3463,11 @@
           <t>Right-of-use asset – Note 7</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.207972</v>
       </c>
@@ -3534,7 +3558,11 @@
           <t>Accounts payable and accrued liabilities – Notes 9 and 12 $</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.268019</v>
       </c>
@@ -3621,7 +3649,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>25.260027</v>
       </c>
@@ -3650,7 +3682,11 @@
           <t>Reserves – Note 10</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>3.149222</v>
       </c>
@@ -4872,7 +4908,11 @@
           <t>Depreciation – Notes 7 and 8</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -4961,7 +5001,11 @@
           <t>Professional fees – Note 13</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5292,7 +5336,11 @@
           <t>Loss per share – basic and diluted – Note 12 $</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -5350,7 +5398,11 @@
           <t>Depreciation – Notes 6 and 7</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>0.056958</v>
       </c>
@@ -5408,7 +5460,11 @@
           <t>Professional fees – Note 12</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>0.137672</v>
       </c>
@@ -5495,7 +5551,11 @@
           <t>Loss per share – basic and diluted – Note 11 $</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>-1e-08</v>
       </c>

--- a/output/pdf_financials_xlsx/CRUZ.xlsx
+++ b/output/pdf_financials_xlsx/CRUZ.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.16183</v>
+        <v>0.32493</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.130844</v>
+        <v>0.295944</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.183488</v>
+        <v>0.362988</v>
       </c>
     </row>
     <row r="8">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.2203</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.2231</v>
       </c>
     </row>
     <row r="68">
@@ -4941,7 +4941,11 @@
           <t>Management and directors’ fees – Note 13</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -5431,7 +5435,11 @@
           <t>Management and directors’ fees – Note 12</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.1631</v>
       </c>
